--- a/LISTAS/mi/MIRADOR OPTICO.xlsx
+++ b/LISTAS/mi/MIRADOR OPTICO.xlsx
@@ -782,14 +782,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="20" t="n">
-        <v>45163.60892720671</v>
+        <v>45253</v>
       </c>
       <c r="E1" s="7" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -830,15 +826,6 @@
     <row r="11" ht="41.25" customHeight="1" s="1">
       <c r="E11" s="10" t="n"/>
     </row>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
     <row r="21" ht="18" customHeight="1" s="1">
       <c r="A21" s="14" t="inlineStr">
         <is>
@@ -870,7 +857,7 @@
       </c>
       <c r="C22" s="27" t="n"/>
       <c r="D22" s="29" t="n">
-        <v>1302.529</v>
+        <v>1497.908</v>
       </c>
       <c r="E22" s="30" t="n"/>
       <c r="F22" s="30" t="n"/>
@@ -888,14 +875,11 @@
       </c>
       <c r="C23" s="27" t="n"/>
       <c r="D23" s="29" t="n">
-        <v>1302.529</v>
+        <v>1497.908</v>
       </c>
       <c r="E23" s="30" t="n"/>
       <c r="F23" s="30" t="n"/>
     </row>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
     <row r="27" ht="18" customHeight="1" s="1">
       <c r="E27" s="4" t="n"/>
     </row>
@@ -914,11 +898,6 @@
     <row r="32" ht="18" customHeight="1" s="1">
       <c r="E32" s="4" t="n"/>
     </row>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
     <row r="38">
       <c r="A38" s="13" t="inlineStr">
         <is>
@@ -926,14 +905,6 @@
         </is>
       </c>
     </row>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
     <row r="47" ht="15.75" customHeight="1" s="1">
       <c r="A47" s="5" t="n"/>
     </row>
@@ -942,12 +913,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B23:C23"/>
     <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A9:D9"/>
     <mergeCell ref="A10:D10"/>
-    <mergeCell ref="B21:C21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/MIRADOR OPTICO.xlsx
+++ b/LISTAS/mi/MIRADOR OPTICO.xlsx
@@ -782,7 +782,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="20" t="n">
-        <v>45253</v>
+        <v>45256</v>
       </c>
       <c r="E1" s="7" t="n"/>
     </row>

--- a/LISTAS/mi/MIRADOR OPTICO.xlsx
+++ b/LISTAS/mi/MIRADOR OPTICO.xlsx
@@ -782,7 +782,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="20" t="n">
-        <v>45256</v>
+        <v>45266</v>
       </c>
       <c r="E1" s="7" t="n"/>
     </row>

--- a/LISTAS/mi/MIRADOR OPTICO.xlsx
+++ b/LISTAS/mi/MIRADOR OPTICO.xlsx
@@ -782,10 +782,14 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="20" t="n">
-        <v>45266</v>
+        <v>45261.57773655045</v>
       </c>
       <c r="E1" s="7" t="n"/>
     </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -826,6 +830,15 @@
     <row r="11" ht="41.25" customHeight="1" s="1">
       <c r="E11" s="10" t="n"/>
     </row>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
     <row r="21" ht="18" customHeight="1" s="1">
       <c r="A21" s="14" t="inlineStr">
         <is>
@@ -857,7 +870,7 @@
       </c>
       <c r="C22" s="27" t="n"/>
       <c r="D22" s="29" t="n">
-        <v>1497.908</v>
+        <v>2292.77</v>
       </c>
       <c r="E22" s="30" t="n"/>
       <c r="F22" s="30" t="n"/>
@@ -875,11 +888,14 @@
       </c>
       <c r="C23" s="27" t="n"/>
       <c r="D23" s="29" t="n">
-        <v>1497.908</v>
+        <v>2292.77</v>
       </c>
       <c r="E23" s="30" t="n"/>
       <c r="F23" s="30" t="n"/>
     </row>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
     <row r="27" ht="18" customHeight="1" s="1">
       <c r="E27" s="4" t="n"/>
     </row>
@@ -898,6 +914,11 @@
     <row r="32" ht="18" customHeight="1" s="1">
       <c r="E32" s="4" t="n"/>
     </row>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
     <row r="38">
       <c r="A38" s="13" t="inlineStr">
         <is>
@@ -905,6 +926,14 @@
         </is>
       </c>
     </row>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
     <row r="47" ht="15.75" customHeight="1" s="1">
       <c r="A47" s="5" t="n"/>
     </row>
@@ -913,12 +942,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B23:C23"/>
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A10:D10"/>
     <mergeCell ref="B21:C21"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="A10:D10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/MIRADOR OPTICO.xlsx
+++ b/LISTAS/mi/MIRADOR OPTICO.xlsx
@@ -782,14 +782,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="20" t="n">
-        <v>45261.57773655045</v>
+        <v>45286</v>
       </c>
       <c r="E1" s="7" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -830,15 +826,6 @@
     <row r="11" ht="41.25" customHeight="1" s="1">
       <c r="E11" s="10" t="n"/>
     </row>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
     <row r="21" ht="18" customHeight="1" s="1">
       <c r="A21" s="14" t="inlineStr">
         <is>
@@ -870,7 +857,7 @@
       </c>
       <c r="C22" s="27" t="n"/>
       <c r="D22" s="29" t="n">
-        <v>2292.77</v>
+        <v>1497.908</v>
       </c>
       <c r="E22" s="30" t="n"/>
       <c r="F22" s="30" t="n"/>
@@ -888,14 +875,11 @@
       </c>
       <c r="C23" s="27" t="n"/>
       <c r="D23" s="29" t="n">
-        <v>2292.77</v>
+        <v>1497.908</v>
       </c>
       <c r="E23" s="30" t="n"/>
       <c r="F23" s="30" t="n"/>
     </row>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
     <row r="27" ht="18" customHeight="1" s="1">
       <c r="E27" s="4" t="n"/>
     </row>
@@ -914,11 +898,6 @@
     <row r="32" ht="18" customHeight="1" s="1">
       <c r="E32" s="4" t="n"/>
     </row>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
     <row r="38">
       <c r="A38" s="13" t="inlineStr">
         <is>
@@ -926,14 +905,6 @@
         </is>
       </c>
     </row>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
     <row r="47" ht="15.75" customHeight="1" s="1">
       <c r="A47" s="5" t="n"/>
     </row>
@@ -942,12 +913,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B23:C23"/>
     <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="A1:D1"/>
     <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="B21:C21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
